--- a/Peraltes.xlsx
+++ b/Peraltes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\AppPeraltes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB0A59E-E333-4CC2-B336-9D72C9B41F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1FDF15-14F2-4394-890B-2C5897FA3C46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{8A759261-3CF2-4445-90CB-A52946BBA4E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A759261-3CF2-4445-90CB-A52946BBA4E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Peralte 4%" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="12">
   <si>
     <t>AASHTO 2018 Metric eMax 4%</t>
   </si>
@@ -533,8 +533,8 @@
       <c r="B17" s="1">
         <v>237</v>
       </c>
-      <c r="C17" s="3">
-        <v>0.02</v>
+      <c r="C17" s="3" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
